--- a/Result/checksun/金融業.xlsx
+++ b/Result/checksun/金融業.xlsx
@@ -723,7 +723,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>弱勢突破股</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -773,24 +773,24 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t>0.44</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="O2" t="inlineStr">
         <is>
           <t>-6.0</t>
@@ -803,12 +803,12 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>709</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>9.64</t>
+          <t>9.59</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>81.43</t>
+          <t>81.79</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>4516</t>
+          <t>4536</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>709</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>9.64</t>
+          <t>9.59</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>81.43</t>
+          <t>81.79</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>4516</t>
+          <t>4536</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1379,12 +1379,12 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>709</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>9.64</t>
+          <t>9.59</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>81.43</t>
+          <t>81.79</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1554,12 +1554,12 @@
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>4516</t>
+          <t>4536</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1667,12 +1667,12 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>709</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>9.64</t>
+          <t>9.59</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>81.43</t>
+          <t>81.79</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>4516</t>
+          <t>4536</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>709</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -2105,7 +2105,7 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>9.64</t>
+          <t>9.59</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>81.43</t>
+          <t>81.79</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>4516</t>
+          <t>4536</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
@@ -2213,24 +2213,24 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t>0.44</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="O7" t="inlineStr">
         <is>
           <t>-10.0</t>
@@ -2243,12 +2243,12 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>709</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -2393,7 +2393,7 @@
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>9.64</t>
+          <t>9.59</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>81.43</t>
+          <t>81.79</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>4516</t>
+          <t>4536</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
@@ -2501,24 +2501,24 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t>0.44</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="O8" t="inlineStr">
         <is>
           <t>13.0</t>
@@ -2531,12 +2531,12 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>709</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>9.64</t>
+          <t>9.59</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>81.43</t>
+          <t>81.79</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
@@ -2706,12 +2706,12 @@
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>4516</t>
+          <t>4536</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
@@ -2789,7 +2789,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -2819,12 +2819,12 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>709</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>9.64</t>
+          <t>9.59</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>81.43</t>
+          <t>81.79</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
@@ -2994,12 +2994,12 @@
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>4516</t>
+          <t>4536</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
@@ -3077,24 +3077,24 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
+          <t>0.44</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="O10" t="inlineStr">
         <is>
           <t>27.0</t>
@@ -3107,12 +3107,12 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>709</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -3257,7 +3257,7 @@
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>9.64</t>
+          <t>9.59</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>81.43</t>
+          <t>81.79</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>4516</t>
+          <t>4536</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
@@ -3365,54 +3365,54 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
+          <t>0.87</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>709</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>-0.35</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
           <t>0.44</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>334</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>-0.35</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>0.44</t>
-        </is>
-      </c>
       <c r="U11" t="inlineStr">
         <is>
           <t>1.49</t>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>9.64</t>
+          <t>9.59</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>81.43</t>
+          <t>81.79</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
@@ -3570,12 +3570,12 @@
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>4516</t>
+          <t>4536</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -3683,12 +3683,12 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>709</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -3833,7 +3833,7 @@
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>9.64</t>
+          <t>9.59</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>81.43</t>
+          <t>81.79</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>4516</t>
+          <t>4536</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
@@ -3895,7 +3895,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>強勢股;反彈型股</t>
+          <t>強勢股;【b】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3945,42 +3945,42 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
+          <t>-0.23</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>73</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -4080,7 +4080,7 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>5.43</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>11.39</t>
+          <t>11.36</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
@@ -4150,12 +4150,12 @@
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>28350</t>
+          <t>28286</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
@@ -4233,7 +4233,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -4263,12 +4263,12 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>73</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>5.43</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>11.39</t>
+          <t>11.36</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>28350</t>
+          <t>28286</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>73</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>5.43</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>11.39</t>
+          <t>11.36</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
@@ -4726,12 +4726,12 @@
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>28350</t>
+          <t>28286</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>73</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>5.43</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
@@ -4999,7 +4999,7 @@
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>11.39</t>
+          <t>11.36</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
@@ -5014,12 +5014,12 @@
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>28350</t>
+          <t>28286</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
@@ -5097,7 +5097,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>73</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>5.43</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>11.39</t>
+          <t>11.36</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>28350</t>
+          <t>28286</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
@@ -5385,7 +5385,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -5415,12 +5415,12 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>73</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -5565,7 +5565,7 @@
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>5.43</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
@@ -5575,7 +5575,7 @@
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>11.39</t>
+          <t>11.36</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>28350</t>
+          <t>28286</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -5703,12 +5703,12 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>73</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -5808,7 +5808,7 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>5.43</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>11.39</t>
+          <t>11.36</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
@@ -5878,12 +5878,12 @@
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>28350</t>
+          <t>28286</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
@@ -5961,7 +5961,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -5991,12 +5991,12 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>73</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
@@ -6141,7 +6141,7 @@
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>5.43</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>11.39</t>
+          <t>11.36</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>28350</t>
+          <t>28286</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
@@ -6249,7 +6249,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>4.64</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>73</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -6429,7 +6429,7 @@
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>5.43</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>11.39</t>
+          <t>11.36</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>28350</t>
+          <t>28286</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
@@ -6537,7 +6537,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>4.41</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>73</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -6717,7 +6717,7 @@
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>5.43</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
@@ -6727,7 +6727,7 @@
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>11.39</t>
+          <t>11.36</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
@@ -6742,12 +6742,12 @@
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>28350</t>
+          <t>28286</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -6855,12 +6855,12 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>73</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -7005,7 +7005,7 @@
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>5.43</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>11.39</t>
+          <t>11.36</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
@@ -7030,12 +7030,12 @@
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>28350</t>
+          <t>28286</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
@@ -7067,7 +7067,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>建議關注股</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -7117,24 +7117,24 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="O24" t="inlineStr">
         <is>
           <t>2.0</t>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>182</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -7297,7 +7297,7 @@
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>11.99</t>
+          <t>11.82</t>
         </is>
       </c>
       <c r="AV24" t="inlineStr">
@@ -7322,12 +7322,12 @@
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>6361</t>
+          <t>6455</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
@@ -7405,7 +7405,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -7435,12 +7435,12 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>182</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -7585,7 +7585,7 @@
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>11.99</t>
+          <t>11.82</t>
         </is>
       </c>
       <c r="AV25" t="inlineStr">
@@ -7610,12 +7610,12 @@
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>6361</t>
+          <t>6455</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
@@ -7693,7 +7693,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -7723,12 +7723,12 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>182</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -7873,7 +7873,7 @@
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>11.99</t>
+          <t>11.82</t>
         </is>
       </c>
       <c r="AV26" t="inlineStr">
@@ -7898,12 +7898,12 @@
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>6361</t>
+          <t>6455</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
@@ -7981,7 +7981,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>182</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -8161,7 +8161,7 @@
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>11.99</t>
+          <t>11.82</t>
         </is>
       </c>
       <c r="AV27" t="inlineStr">
@@ -8186,12 +8186,12 @@
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>6361</t>
+          <t>6455</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
@@ -8269,24 +8269,24 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="O28" t="inlineStr">
         <is>
           <t>4.0</t>
@@ -8299,12 +8299,12 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>182</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -8449,7 +8449,7 @@
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>11.99</t>
+          <t>11.82</t>
         </is>
       </c>
       <c r="AV28" t="inlineStr">
@@ -8474,12 +8474,12 @@
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>6361</t>
+          <t>6455</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
@@ -8557,7 +8557,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -8587,12 +8587,12 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>182</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -8737,7 +8737,7 @@
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>11.99</t>
+          <t>11.82</t>
         </is>
       </c>
       <c r="AV29" t="inlineStr">
@@ -8762,12 +8762,12 @@
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>6361</t>
+          <t>6455</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
@@ -8845,7 +8845,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -8875,12 +8875,12 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>182</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -9025,7 +9025,7 @@
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>11.99</t>
+          <t>11.82</t>
         </is>
       </c>
       <c r="AV30" t="inlineStr">
@@ -9050,12 +9050,12 @@
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>6361</t>
+          <t>6455</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
@@ -9133,7 +9133,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>182</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -9313,7 +9313,7 @@
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>11.99</t>
+          <t>11.82</t>
         </is>
       </c>
       <c r="AV31" t="inlineStr">
@@ -9338,12 +9338,12 @@
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>6361</t>
+          <t>6455</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>182</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -9601,7 +9601,7 @@
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>11.99</t>
+          <t>11.82</t>
         </is>
       </c>
       <c r="AV32" t="inlineStr">
@@ -9626,12 +9626,12 @@
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>6361</t>
+          <t>6455</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -9739,12 +9739,12 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>182</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -9889,7 +9889,7 @@
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>11.99</t>
+          <t>11.82</t>
         </is>
       </c>
       <c r="AV33" t="inlineStr">
@@ -9914,12 +9914,12 @@
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>6361</t>
+          <t>6455</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
@@ -9997,7 +9997,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -10027,12 +10027,12 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>182</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -10177,7 +10177,7 @@
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>11.99</t>
+          <t>11.82</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
@@ -10202,12 +10202,12 @@
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>6361</t>
+          <t>6455</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
@@ -10239,7 +10239,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>弱勢突破股</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -10319,12 +10319,12 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -10494,7 +10494,7 @@
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
@@ -10607,12 +10607,12 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -10782,7 +10782,7 @@
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA36" t="inlineStr">
@@ -10895,12 +10895,12 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -11070,7 +11070,7 @@
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA37" t="inlineStr">
@@ -11183,12 +11183,12 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -11358,7 +11358,7 @@
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA38" t="inlineStr">
@@ -11471,12 +11471,12 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -11646,7 +11646,7 @@
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA39" t="inlineStr">
@@ -11759,12 +11759,12 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA40" t="inlineStr">
@@ -12047,12 +12047,12 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -12222,7 +12222,7 @@
       </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA41" t="inlineStr">
@@ -12335,12 +12335,12 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -12510,7 +12510,7 @@
       </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA42" t="inlineStr">
@@ -12623,12 +12623,12 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -12798,7 +12798,7 @@
       </c>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA43" t="inlineStr">
@@ -12911,12 +12911,12 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -13086,7 +13086,7 @@
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA44" t="inlineStr">
@@ -13199,12 +13199,12 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -13374,7 +13374,7 @@
       </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA45" t="inlineStr">
@@ -13411,7 +13411,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>強勢股;反彈型股</t>
+          <t>強勢股;【b】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -13461,24 +13461,24 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="O46" t="inlineStr">
         <is>
           <t>5.0</t>
@@ -13491,12 +13491,12 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>1541</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -13596,7 +13596,7 @@
       </c>
       <c r="AL46" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM46" t="inlineStr">
@@ -13641,7 +13641,7 @@
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>9.92</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="AV46" t="inlineStr">
@@ -13666,12 +13666,12 @@
       </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
-          <t>8479</t>
+          <t>8617</t>
         </is>
       </c>
       <c r="BB46" t="inlineStr">
@@ -13686,7 +13686,7 @@
       </c>
       <c r="BD46" t="inlineStr">
         <is>
-          <t>金融業右下</t>
+          <t>金融業平</t>
         </is>
       </c>
       <c r="BE46" t="inlineStr">
@@ -13749,7 +13749,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -13779,12 +13779,12 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>1541</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -13884,7 +13884,7 @@
       </c>
       <c r="AL47" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM47" t="inlineStr">
@@ -13929,7 +13929,7 @@
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>9.92</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="AV47" t="inlineStr">
@@ -13954,12 +13954,12 @@
       </c>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
-          <t>8479</t>
+          <t>8617</t>
         </is>
       </c>
       <c r="BB47" t="inlineStr">
@@ -13974,7 +13974,7 @@
       </c>
       <c r="BD47" t="inlineStr">
         <is>
-          <t>金融業右下</t>
+          <t>金融業平</t>
         </is>
       </c>
       <c r="BE47" t="inlineStr">
@@ -14037,7 +14037,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -14067,12 +14067,12 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>1541</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -14172,7 +14172,7 @@
       </c>
       <c r="AL48" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
@@ -14217,7 +14217,7 @@
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>9.92</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="AV48" t="inlineStr">
@@ -14242,12 +14242,12 @@
       </c>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
-          <t>8479</t>
+          <t>8617</t>
         </is>
       </c>
       <c r="BB48" t="inlineStr">
@@ -14262,7 +14262,7 @@
       </c>
       <c r="BD48" t="inlineStr">
         <is>
-          <t>金融業右下</t>
+          <t>金融業平</t>
         </is>
       </c>
       <c r="BE48" t="inlineStr">
@@ -14325,187 +14325,187 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
+          <t>2.39</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>-11.0</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>價-量縮</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>1541</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>4.26</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>-1.03</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>12.05</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>11.5575</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>11.678</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>512.01</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>0.12</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>94.87179487179479</t>
+        </is>
+      </c>
+      <c r="AD49" t="inlineStr">
+        <is>
+          <t>16.65</t>
+        </is>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>12115.8</t>
+        </is>
+      </c>
+      <c r="AG49" t="inlineStr">
+        <is>
+          <t>10386.3</t>
+        </is>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>1541.642688805734</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>2355.69</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AL49" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>康和證</t>
+        </is>
+      </c>
+      <c r="AN49" t="inlineStr">
+        <is>
+          <t>金融業</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="AP49" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="AQ49" t="inlineStr">
+        <is>
+          <t>15.49170048247436</t>
+        </is>
+      </c>
+      <c r="AR49" t="inlineStr">
+        <is>
+          <t>666.6865521264185</t>
+        </is>
+      </c>
+      <c r="AS49" t="inlineStr">
+        <is>
+          <t>-47.11211874687458</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr">
+        <is>
           <t>0.81</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>-11.0</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>價-量縮</t>
-        </is>
-      </c>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R49" t="inlineStr">
-        <is>
-          <t>1319</t>
-        </is>
-      </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>1.66</t>
-        </is>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>4.26</t>
-        </is>
-      </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>-1.03</t>
-        </is>
-      </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>12.05</t>
-        </is>
-      </c>
-      <c r="W49" t="inlineStr">
-        <is>
-          <t>11.5575</t>
-        </is>
-      </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>11.678</t>
-        </is>
-      </c>
-      <c r="Y49" t="inlineStr">
-        <is>
-          <t>512.01</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>0.12</t>
-        </is>
-      </c>
-      <c r="AA49" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>94.87179487179479</t>
-        </is>
-      </c>
-      <c r="AD49" t="inlineStr">
-        <is>
-          <t>16.65</t>
-        </is>
-      </c>
-      <c r="AE49" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AF49" t="inlineStr">
-        <is>
-          <t>12115.8</t>
-        </is>
-      </c>
-      <c r="AG49" t="inlineStr">
-        <is>
-          <t>10386.3</t>
-        </is>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>1541.642688805734</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>2355.69</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AL49" t="inlineStr">
-        <is>
-          <t>2025-09-05</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>康和證</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>金融業</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="AP49" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="AQ49" t="inlineStr">
-        <is>
-          <t>15.49170048247436</t>
-        </is>
-      </c>
-      <c r="AR49" t="inlineStr">
-        <is>
-          <t>666.6865521264185</t>
-        </is>
-      </c>
-      <c r="AS49" t="inlineStr">
-        <is>
-          <t>-47.11211874687458</t>
-        </is>
-      </c>
-      <c r="AT49" t="inlineStr">
-        <is>
-          <t>0.81</t>
-        </is>
-      </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>9.92</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="AV49" t="inlineStr">
@@ -14530,12 +14530,12 @@
       </c>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
-          <t>8479</t>
+          <t>8617</t>
         </is>
       </c>
       <c r="BB49" t="inlineStr">
@@ -14550,7 +14550,7 @@
       </c>
       <c r="BD49" t="inlineStr">
         <is>
-          <t>金融業右下</t>
+          <t>金融業平</t>
         </is>
       </c>
       <c r="BE49" t="inlineStr">
@@ -14613,7 +14613,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -14643,12 +14643,12 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>1541</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -14748,7 +14748,7 @@
       </c>
       <c r="AL50" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM50" t="inlineStr">
@@ -14793,7 +14793,7 @@
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>9.92</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="AV50" t="inlineStr">
@@ -14818,12 +14818,12 @@
       </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
-          <t>8479</t>
+          <t>8617</t>
         </is>
       </c>
       <c r="BB50" t="inlineStr">
@@ -14838,7 +14838,7 @@
       </c>
       <c r="BD50" t="inlineStr">
         <is>
-          <t>金融業右下</t>
+          <t>金融業平</t>
         </is>
       </c>
       <c r="BE50" t="inlineStr">
@@ -14901,7 +14901,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>4.78</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -14931,12 +14931,12 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>1541</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -15036,7 +15036,7 @@
       </c>
       <c r="AL51" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM51" t="inlineStr">
@@ -15081,7 +15081,7 @@
       </c>
       <c r="AU51" t="inlineStr">
         <is>
-          <t>9.92</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="AV51" t="inlineStr">
@@ -15106,12 +15106,12 @@
       </c>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
-          <t>8479</t>
+          <t>8617</t>
         </is>
       </c>
       <c r="BB51" t="inlineStr">
@@ -15126,7 +15126,7 @@
       </c>
       <c r="BD51" t="inlineStr">
         <is>
-          <t>金融業右下</t>
+          <t>金融業平</t>
         </is>
       </c>
       <c r="BE51" t="inlineStr">
@@ -15189,7 +15189,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -15219,12 +15219,12 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>1541</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -15324,7 +15324,7 @@
       </c>
       <c r="AL52" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM52" t="inlineStr">
@@ -15369,7 +15369,7 @@
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>9.92</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="AV52" t="inlineStr">
@@ -15394,12 +15394,12 @@
       </c>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
-          <t>8479</t>
+          <t>8617</t>
         </is>
       </c>
       <c r="BB52" t="inlineStr">
@@ -15414,7 +15414,7 @@
       </c>
       <c r="BD52" t="inlineStr">
         <is>
-          <t>金融業右下</t>
+          <t>金融業平</t>
         </is>
       </c>
       <c r="BE52" t="inlineStr">
@@ -15477,7 +15477,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>5.98</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -15507,12 +15507,12 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>1541</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -15612,7 +15612,7 @@
       </c>
       <c r="AL53" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM53" t="inlineStr">
@@ -15657,7 +15657,7 @@
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>9.92</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="AV53" t="inlineStr">
@@ -15682,12 +15682,12 @@
       </c>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
-          <t>8479</t>
+          <t>8617</t>
         </is>
       </c>
       <c r="BB53" t="inlineStr">
@@ -15702,7 +15702,7 @@
       </c>
       <c r="BD53" t="inlineStr">
         <is>
-          <t>金融業右下</t>
+          <t>金融業平</t>
         </is>
       </c>
       <c r="BE53" t="inlineStr">
@@ -15765,7 +15765,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>7.57</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -15795,12 +15795,12 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>1541</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
@@ -15900,7 +15900,7 @@
       </c>
       <c r="AL54" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM54" t="inlineStr">
@@ -15945,7 +15945,7 @@
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>9.92</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="AV54" t="inlineStr">
@@ -15970,12 +15970,12 @@
       </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
-          <t>8479</t>
+          <t>8617</t>
         </is>
       </c>
       <c r="BB54" t="inlineStr">
@@ -15990,7 +15990,7 @@
       </c>
       <c r="BD54" t="inlineStr">
         <is>
-          <t>金融業右下</t>
+          <t>金融業平</t>
         </is>
       </c>
       <c r="BE54" t="inlineStr">
@@ -16053,7 +16053,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>7.29</t>
+          <t>8.76</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -16083,12 +16083,12 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>1541</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -16233,7 +16233,7 @@
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>9.92</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="AV55" t="inlineStr">
@@ -16258,12 +16258,12 @@
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
-          <t>8479</t>
+          <t>8617</t>
         </is>
       </c>
       <c r="BB55" t="inlineStr">
@@ -16278,7 +16278,7 @@
       </c>
       <c r="BD55" t="inlineStr">
         <is>
-          <t>金融業右下</t>
+          <t>金融業平</t>
         </is>
       </c>
       <c r="BE55" t="inlineStr">
@@ -16341,7 +16341,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>6.88</t>
+          <t>8.37</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -16371,12 +16371,12 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>1541</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -16521,7 +16521,7 @@
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>9.92</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="AV56" t="inlineStr">
@@ -16546,12 +16546,12 @@
       </c>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
-          <t>8479</t>
+          <t>8617</t>
         </is>
       </c>
       <c r="BB56" t="inlineStr">
@@ -16566,7 +16566,7 @@
       </c>
       <c r="BD56" t="inlineStr">
         <is>
-          <t>金融業右下</t>
+          <t>金融業平</t>
         </is>
       </c>
       <c r="BE56" t="inlineStr">
@@ -16583,7 +16583,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>弱勢突破股</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -16633,187 +16633,187 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>-3.0</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>-0.74</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>-1.14</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>10.88</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>11.005</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>10.915</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>-218.53</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>-3.0</t>
-        </is>
-      </c>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="Q57" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R57" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>-0.74</t>
-        </is>
-      </c>
-      <c r="T57" t="inlineStr">
-        <is>
-          <t>-1.14</t>
-        </is>
-      </c>
-      <c r="U57" t="inlineStr">
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AD57" t="inlineStr">
+        <is>
+          <t>49.24</t>
+        </is>
+      </c>
+      <c r="AE57" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AF57" t="inlineStr">
+        <is>
+          <t>-1164.4</t>
+        </is>
+      </c>
+      <c r="AG57" t="inlineStr">
+        <is>
+          <t>-2294.0</t>
+        </is>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>-49</t>
+        </is>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>-282.5038872978652</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>-214.0</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>宏遠證</t>
+        </is>
+      </c>
+      <c r="AN57" t="inlineStr">
+        <is>
+          <t>金融業</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="AP57" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="AQ57" t="inlineStr">
+        <is>
+          <t>-14.70073965570709</t>
+        </is>
+      </c>
+      <c r="AR57" t="inlineStr">
+        <is>
+          <t>13.4167953396968</t>
+        </is>
+      </c>
+      <c r="AS57" t="inlineStr">
+        <is>
+          <t>-49.23563293456245</t>
+        </is>
+      </c>
+      <c r="AT57" t="inlineStr">
         <is>
           <t>0.82</t>
         </is>
       </c>
-      <c r="V57" t="inlineStr">
-        <is>
-          <t>10.88</t>
-        </is>
-      </c>
-      <c r="W57" t="inlineStr">
-        <is>
-          <t>11.005</t>
-        </is>
-      </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>10.915</t>
-        </is>
-      </c>
-      <c r="Y57" t="inlineStr">
-        <is>
-          <t>-218.53</t>
-        </is>
-      </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
-      <c r="AA57" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AD57" t="inlineStr">
-        <is>
-          <t>49.24</t>
-        </is>
-      </c>
-      <c r="AE57" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AF57" t="inlineStr">
-        <is>
-          <t>-1164.4</t>
-        </is>
-      </c>
-      <c r="AG57" t="inlineStr">
-        <is>
-          <t>-2294.0</t>
-        </is>
-      </c>
-      <c r="AH57" t="inlineStr">
-        <is>
-          <t>-49</t>
-        </is>
-      </c>
-      <c r="AI57" t="inlineStr">
-        <is>
-          <t>-282.5038872978652</t>
-        </is>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>-214.0</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL57" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>宏遠證</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>金融業</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="AP57" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="AQ57" t="inlineStr">
-        <is>
-          <t>-14.70073965570709</t>
-        </is>
-      </c>
-      <c r="AR57" t="inlineStr">
-        <is>
-          <t>13.4167953396968</t>
-        </is>
-      </c>
-      <c r="AS57" t="inlineStr">
-        <is>
-          <t>-49.23563293456245</t>
-        </is>
-      </c>
-      <c r="AT57" t="inlineStr">
-        <is>
-          <t>0.82</t>
-        </is>
-      </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AV57" t="inlineStr">
@@ -16838,12 +16838,12 @@
       </c>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
-          <t>4233</t>
+          <t>4291</t>
         </is>
       </c>
       <c r="BB57" t="inlineStr">
@@ -16921,99 +16921,99 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>-3.0</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>-0.92</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>-1.16</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>1.04</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>10.9</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>11.0275</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>10.914</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>-134.87</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>-2</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>-3.0</t>
-        </is>
-      </c>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="Q58" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R58" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>-0.92</t>
-        </is>
-      </c>
-      <c r="T58" t="inlineStr">
-        <is>
-          <t>-1.16</t>
-        </is>
-      </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>1.04</t>
-        </is>
-      </c>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>10.9</t>
-        </is>
-      </c>
-      <c r="W58" t="inlineStr">
-        <is>
-          <t>11.0275</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>10.914</t>
-        </is>
-      </c>
-      <c r="Y58" t="inlineStr">
-        <is>
-          <t>-134.87</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
-      <c r="AA58" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
+      <c r="AC58" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AD58" t="inlineStr">
         <is>
           <t>30.37</t>
@@ -17101,7 +17101,7 @@
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AV58" t="inlineStr">
@@ -17126,12 +17126,12 @@
       </c>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
-          <t>4233</t>
+          <t>4291</t>
         </is>
       </c>
       <c r="BB58" t="inlineStr">
@@ -17209,7 +17209,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -17239,12 +17239,12 @@
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>221</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -17389,7 +17389,7 @@
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AV59" t="inlineStr">
@@ -17414,12 +17414,12 @@
       </c>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
-          <t>4233</t>
+          <t>4291</t>
         </is>
       </c>
       <c r="BB59" t="inlineStr">
@@ -17497,7 +17497,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -17527,12 +17527,12 @@
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>221</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -17677,7 +17677,7 @@
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AV60" t="inlineStr">
@@ -17702,12 +17702,12 @@
       </c>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
-          <t>4233</t>
+          <t>4291</t>
         </is>
       </c>
       <c r="BB60" t="inlineStr">
@@ -17785,7 +17785,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -17815,12 +17815,12 @@
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>221</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
@@ -17965,7 +17965,7 @@
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AV61" t="inlineStr">
@@ -17990,12 +17990,12 @@
       </c>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
-          <t>4233</t>
+          <t>4291</t>
         </is>
       </c>
       <c r="BB61" t="inlineStr">
@@ -18073,7 +18073,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -18103,12 +18103,12 @@
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>221</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
@@ -18253,7 +18253,7 @@
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AV62" t="inlineStr">
@@ -18278,12 +18278,12 @@
       </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
-          <t>4233</t>
+          <t>4291</t>
         </is>
       </c>
       <c r="BB62" t="inlineStr">
@@ -18361,7 +18361,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -18391,12 +18391,12 @@
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>221</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
@@ -18541,7 +18541,7 @@
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AV63" t="inlineStr">
@@ -18566,12 +18566,12 @@
       </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
-          <t>4233</t>
+          <t>4291</t>
         </is>
       </c>
       <c r="BB63" t="inlineStr">
@@ -18649,7 +18649,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -18679,12 +18679,12 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>221</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
@@ -18829,7 +18829,7 @@
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AV64" t="inlineStr">
@@ -18854,12 +18854,12 @@
       </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
-          <t>4233</t>
+          <t>4291</t>
         </is>
       </c>
       <c r="BB64" t="inlineStr">
@@ -18937,7 +18937,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -18967,12 +18967,12 @@
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>221</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
@@ -19117,7 +19117,7 @@
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AV65" t="inlineStr">
@@ -19142,12 +19142,12 @@
       </c>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
-          <t>4233</t>
+          <t>4291</t>
         </is>
       </c>
       <c r="BB65" t="inlineStr">
@@ -19225,7 +19225,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -19255,12 +19255,12 @@
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>221</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
@@ -19405,7 +19405,7 @@
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AV66" t="inlineStr">
@@ -19430,12 +19430,12 @@
       </c>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
-          <t>4233</t>
+          <t>4291</t>
         </is>
       </c>
       <c r="BB66" t="inlineStr">
@@ -19513,7 +19513,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -19543,12 +19543,12 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>221</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
@@ -19693,7 +19693,7 @@
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AV67" t="inlineStr">
@@ -19718,12 +19718,12 @@
       </c>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
-          <t>4233</t>
+          <t>4291</t>
         </is>
       </c>
       <c r="BB67" t="inlineStr">
@@ -19755,7 +19755,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>弱勢突破股</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -19805,7 +19805,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -19835,12 +19835,12 @@
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>22</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -19985,7 +19985,7 @@
       </c>
       <c r="AU68" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AV68" t="inlineStr">
@@ -19995,7 +19995,7 @@
       </c>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>15.44</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
@@ -20010,12 +20010,12 @@
       </c>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
-          <t>1051</t>
+          <t>1047</t>
         </is>
       </c>
       <c r="BB68" t="inlineStr">
@@ -20093,7 +20093,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -20123,12 +20123,12 @@
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>22</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
@@ -20273,7 +20273,7 @@
       </c>
       <c r="AU69" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AV69" t="inlineStr">
@@ -20283,7 +20283,7 @@
       </c>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>15.44</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
@@ -20298,12 +20298,12 @@
       </c>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
-          <t>1051</t>
+          <t>1047</t>
         </is>
       </c>
       <c r="BB69" t="inlineStr">
@@ -20381,7 +20381,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -20411,12 +20411,12 @@
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>22</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
@@ -20561,7 +20561,7 @@
       </c>
       <c r="AU70" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AV70" t="inlineStr">
@@ -20571,7 +20571,7 @@
       </c>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>15.44</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
@@ -20586,12 +20586,12 @@
       </c>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
-          <t>1051</t>
+          <t>1047</t>
         </is>
       </c>
       <c r="BB70" t="inlineStr">
@@ -20669,7 +20669,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -20699,12 +20699,12 @@
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>22</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
@@ -20849,7 +20849,7 @@
       </c>
       <c r="AU71" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AV71" t="inlineStr">
@@ -20859,7 +20859,7 @@
       </c>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>15.44</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
@@ -20874,12 +20874,12 @@
       </c>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
-          <t>1051</t>
+          <t>1047</t>
         </is>
       </c>
       <c r="BB71" t="inlineStr">
@@ -20957,7 +20957,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -20987,12 +20987,12 @@
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>22</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
@@ -21137,7 +21137,7 @@
       </c>
       <c r="AU72" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AV72" t="inlineStr">
@@ -21147,7 +21147,7 @@
       </c>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>15.44</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
@@ -21162,12 +21162,12 @@
       </c>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
-          <t>1051</t>
+          <t>1047</t>
         </is>
       </c>
       <c r="BB72" t="inlineStr">
@@ -21245,7 +21245,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -21275,12 +21275,12 @@
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>22</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
@@ -21425,7 +21425,7 @@
       </c>
       <c r="AU73" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AV73" t="inlineStr">
@@ -21435,7 +21435,7 @@
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>15.44</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
@@ -21450,12 +21450,12 @@
       </c>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
-          <t>1051</t>
+          <t>1047</t>
         </is>
       </c>
       <c r="BB73" t="inlineStr">
@@ -21533,7 +21533,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -21563,12 +21563,12 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>22</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
@@ -21713,7 +21713,7 @@
       </c>
       <c r="AU74" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AV74" t="inlineStr">
@@ -21723,7 +21723,7 @@
       </c>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>15.44</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
@@ -21738,12 +21738,12 @@
       </c>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
-          <t>1051</t>
+          <t>1047</t>
         </is>
       </c>
       <c r="BB74" t="inlineStr">
@@ -21821,7 +21821,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -21851,12 +21851,12 @@
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>22</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
@@ -22001,7 +22001,7 @@
       </c>
       <c r="AU75" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AV75" t="inlineStr">
@@ -22011,7 +22011,7 @@
       </c>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>15.44</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
@@ -22026,12 +22026,12 @@
       </c>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
-          <t>1051</t>
+          <t>1047</t>
         </is>
       </c>
       <c r="BB75" t="inlineStr">
@@ -22109,7 +22109,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -22139,12 +22139,12 @@
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>22</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
@@ -22289,7 +22289,7 @@
       </c>
       <c r="AU76" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AV76" t="inlineStr">
@@ -22299,7 +22299,7 @@
       </c>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>15.44</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
@@ -22314,12 +22314,12 @@
       </c>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
-          <t>1051</t>
+          <t>1047</t>
         </is>
       </c>
       <c r="BB76" t="inlineStr">
@@ -22397,7 +22397,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -22427,12 +22427,12 @@
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>22</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
@@ -22577,7 +22577,7 @@
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AV77" t="inlineStr">
@@ -22587,7 +22587,7 @@
       </c>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>15.44</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
@@ -22602,12 +22602,12 @@
       </c>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
-          <t>1051</t>
+          <t>1047</t>
         </is>
       </c>
       <c r="BB77" t="inlineStr">
@@ -22685,7 +22685,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -22715,12 +22715,12 @@
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>22</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
@@ -22865,7 +22865,7 @@
       </c>
       <c r="AU78" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AV78" t="inlineStr">
@@ -22875,7 +22875,7 @@
       </c>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>15.44</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
@@ -22890,12 +22890,12 @@
       </c>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
-          <t>1051</t>
+          <t>1047</t>
         </is>
       </c>
       <c r="BB78" t="inlineStr">
@@ -22927,7 +22927,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>強勢股;反彈型股</t>
+          <t>強勢股;【b】</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -22977,7 +22977,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -23007,12 +23007,12 @@
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
@@ -23112,7 +23112,7 @@
       </c>
       <c r="AL79" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM79" t="inlineStr">
@@ -23157,7 +23157,7 @@
       </c>
       <c r="AU79" t="inlineStr">
         <is>
-          <t>8.54</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="AV79" t="inlineStr">
@@ -23182,12 +23182,12 @@
       </c>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
-          <t>6386</t>
+          <t>6454</t>
         </is>
       </c>
       <c r="BB79" t="inlineStr">
@@ -23265,7 +23265,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -23295,12 +23295,12 @@
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
@@ -23400,7 +23400,7 @@
       </c>
       <c r="AL80" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM80" t="inlineStr">
@@ -23445,7 +23445,7 @@
       </c>
       <c r="AU80" t="inlineStr">
         <is>
-          <t>8.54</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="AV80" t="inlineStr">
@@ -23470,12 +23470,12 @@
       </c>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
-          <t>6386</t>
+          <t>6454</t>
         </is>
       </c>
       <c r="BB80" t="inlineStr">
@@ -23553,7 +23553,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -23583,12 +23583,12 @@
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
@@ -23688,7 +23688,7 @@
       </c>
       <c r="AL81" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM81" t="inlineStr">
@@ -23733,7 +23733,7 @@
       </c>
       <c r="AU81" t="inlineStr">
         <is>
-          <t>8.54</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="AV81" t="inlineStr">
@@ -23758,12 +23758,12 @@
       </c>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
-          <t>6386</t>
+          <t>6454</t>
         </is>
       </c>
       <c r="BB81" t="inlineStr">
@@ -23841,7 +23841,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -23871,12 +23871,12 @@
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
@@ -23976,7 +23976,7 @@
       </c>
       <c r="AL82" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM82" t="inlineStr">
@@ -24021,7 +24021,7 @@
       </c>
       <c r="AU82" t="inlineStr">
         <is>
-          <t>8.54</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="AV82" t="inlineStr">
@@ -24046,12 +24046,12 @@
       </c>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
-          <t>6386</t>
+          <t>6454</t>
         </is>
       </c>
       <c r="BB82" t="inlineStr">
@@ -24129,7 +24129,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -24159,12 +24159,12 @@
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
@@ -24264,7 +24264,7 @@
       </c>
       <c r="AL83" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM83" t="inlineStr">
@@ -24309,7 +24309,7 @@
       </c>
       <c r="AU83" t="inlineStr">
         <is>
-          <t>8.54</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="AV83" t="inlineStr">
@@ -24334,12 +24334,12 @@
       </c>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
-          <t>6386</t>
+          <t>6454</t>
         </is>
       </c>
       <c r="BB83" t="inlineStr">
@@ -24417,7 +24417,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -24447,12 +24447,12 @@
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
@@ -24552,7 +24552,7 @@
       </c>
       <c r="AL84" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM84" t="inlineStr">
@@ -24597,7 +24597,7 @@
       </c>
       <c r="AU84" t="inlineStr">
         <is>
-          <t>8.54</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="AV84" t="inlineStr">
@@ -24622,12 +24622,12 @@
       </c>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
-          <t>6386</t>
+          <t>6454</t>
         </is>
       </c>
       <c r="BB84" t="inlineStr">
@@ -24705,7 +24705,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -24735,12 +24735,12 @@
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
@@ -24840,7 +24840,7 @@
       </c>
       <c r="AL85" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM85" t="inlineStr">
@@ -24885,7 +24885,7 @@
       </c>
       <c r="AU85" t="inlineStr">
         <is>
-          <t>8.54</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="AV85" t="inlineStr">
@@ -24910,12 +24910,12 @@
       </c>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
-          <t>6386</t>
+          <t>6454</t>
         </is>
       </c>
       <c r="BB85" t="inlineStr">
@@ -24993,7 +24993,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -25023,12 +25023,12 @@
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
@@ -25128,7 +25128,7 @@
       </c>
       <c r="AL86" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM86" t="inlineStr">
@@ -25173,7 +25173,7 @@
       </c>
       <c r="AU86" t="inlineStr">
         <is>
-          <t>8.54</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="AV86" t="inlineStr">
@@ -25198,12 +25198,12 @@
       </c>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
-          <t>6386</t>
+          <t>6454</t>
         </is>
       </c>
       <c r="BB86" t="inlineStr">
@@ -25281,7 +25281,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -25311,12 +25311,12 @@
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
@@ -25416,7 +25416,7 @@
       </c>
       <c r="AL87" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM87" t="inlineStr">
@@ -25461,7 +25461,7 @@
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>8.54</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="AV87" t="inlineStr">
@@ -25486,12 +25486,12 @@
       </c>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
-          <t>6386</t>
+          <t>6454</t>
         </is>
       </c>
       <c r="BB87" t="inlineStr">
@@ -25569,7 +25569,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>6.69</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -25599,12 +25599,12 @@
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
@@ -25704,7 +25704,7 @@
       </c>
       <c r="AL88" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM88" t="inlineStr">
@@ -25749,7 +25749,7 @@
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>8.54</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="AV88" t="inlineStr">
@@ -25774,12 +25774,12 @@
       </c>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
-          <t>6386</t>
+          <t>6454</t>
         </is>
       </c>
       <c r="BB88" t="inlineStr">
@@ -25857,7 +25857,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>6.69</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -25887,12 +25887,12 @@
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
@@ -25992,7 +25992,7 @@
       </c>
       <c r="AL89" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM89" t="inlineStr">
@@ -26037,7 +26037,7 @@
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>8.54</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="AV89" t="inlineStr">
@@ -26062,12 +26062,12 @@
       </c>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
-          <t>6386</t>
+          <t>6454</t>
         </is>
       </c>
       <c r="BB89" t="inlineStr">

--- a/Result/checksun/金融業.xlsx
+++ b/Result/checksun/金融業.xlsx
@@ -1013,7 +1013,11 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -1301,7 +1305,11 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -1589,7 +1597,11 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -1877,7 +1889,11 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -2165,7 +2181,11 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -2453,7 +2473,11 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -2741,7 +2765,11 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -3029,7 +3057,11 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -3317,7 +3349,11 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -3605,7 +3641,11 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -4185,7 +4225,11 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -4473,7 +4517,11 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -4761,7 +4809,11 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -5049,7 +5101,11 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -5337,7 +5393,11 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -5625,7 +5685,11 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -5913,7 +5977,11 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -6201,7 +6269,11 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -6489,7 +6561,11 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -6777,7 +6853,11 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr"/>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -7357,7 +7437,11 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr"/>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -7645,7 +7729,11 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr"/>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -7933,7 +8021,11 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr"/>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -8221,7 +8313,11 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr"/>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -8509,7 +8605,11 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr"/>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -8797,7 +8897,11 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr"/>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -9085,7 +9189,11 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr"/>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -9373,7 +9481,11 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr"/>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -9661,7 +9773,11 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -9949,7 +10065,11 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr"/>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -10529,7 +10649,11 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr"/>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -10817,7 +10941,11 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr"/>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -11105,7 +11233,11 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr"/>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -11393,7 +11525,11 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr"/>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -11681,7 +11817,11 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr"/>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -11969,7 +12109,11 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr"/>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -12257,7 +12401,11 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr"/>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -12545,7 +12693,11 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr"/>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -12833,7 +12985,11 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr"/>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -13121,7 +13277,11 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr"/>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -13701,7 +13861,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr"/>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -13989,7 +14153,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr"/>
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -14277,7 +14445,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr"/>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -14565,7 +14737,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr"/>
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -14853,7 +15029,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr"/>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -15141,7 +15321,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr"/>
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -15429,7 +15613,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr"/>
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -15717,7 +15905,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr"/>
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -16005,7 +16197,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr"/>
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -16293,7 +16489,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr"/>
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -16873,7 +17073,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr"/>
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -17161,7 +17365,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr"/>
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -17449,7 +17657,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr"/>
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -17737,7 +17949,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr"/>
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -18025,7 +18241,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr"/>
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -18313,7 +18533,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr"/>
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -18601,7 +18825,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr"/>
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -18889,7 +19117,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr"/>
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -19177,7 +19409,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr"/>
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -19465,7 +19701,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr"/>
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B67" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -20045,7 +20285,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr"/>
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -20333,7 +20577,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr"/>
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -20621,7 +20869,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr"/>
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -20909,7 +21161,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr"/>
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -21197,7 +21453,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr"/>
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -21485,7 +21745,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr"/>
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -21773,7 +22037,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr"/>
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -22061,7 +22329,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr"/>
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -22349,7 +22621,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr"/>
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -22637,7 +22913,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr"/>
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -23217,7 +23497,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr"/>
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B80" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -23505,7 +23789,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr"/>
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B81" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -23793,7 +24081,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr"/>
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B82" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -24081,7 +24373,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr"/>
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B83" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -24369,7 +24665,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr"/>
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B84" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -24657,7 +24957,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr"/>
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B85" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -24945,7 +25249,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr"/>
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B86" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -25233,7 +25541,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr"/>
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B87" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -25521,7 +25833,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr"/>
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B88" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -25809,7 +26125,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr"/>
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B89" t="inlineStr">
         <is>
           <t>2025-08-25</t>

--- a/Result/checksun/金融業.xlsx
+++ b/Result/checksun/金融業.xlsx
@@ -1011,15 +1011,11 @@
           <t>11.6475</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>11.49</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>11.385</t>
-        </is>
+      <c r="AN2" t="n">
+        <v>11.49</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>11.385</v>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
@@ -1398,15 +1394,11 @@
           <t>11.6175</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>11.481</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>11.37375</t>
-        </is>
+      <c r="AN3" t="n">
+        <v>11.481</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>11.37375</v>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
@@ -1785,15 +1777,11 @@
           <t>11.58</t>
         </is>
       </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>11.47</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>11.360625</t>
-        </is>
+      <c r="AN4" t="n">
+        <v>11.47</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>11.360625</v>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
@@ -2172,15 +2160,11 @@
           <t>11.555</t>
         </is>
       </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>11.464</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>11.350625</t>
-        </is>
+      <c r="AN5" t="n">
+        <v>11.464</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>11.350625</v>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
@@ -2559,15 +2543,11 @@
           <t>11.52</t>
         </is>
       </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>11.452</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>11.3375</t>
-        </is>
+      <c r="AN6" t="n">
+        <v>11.452</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>11.3375</v>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
@@ -2946,15 +2926,11 @@
           <t>11.4875</t>
         </is>
       </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>11.444</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>11.325625</t>
-        </is>
+      <c r="AN7" t="n">
+        <v>11.444</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>11.325625</v>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
@@ -3333,15 +3309,11 @@
           <t>11.4675</t>
         </is>
       </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>11.443</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>11.3175</t>
-        </is>
+      <c r="AN8" t="n">
+        <v>11.443</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>11.3175</v>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
@@ -3720,15 +3692,11 @@
           <t>11.445</t>
         </is>
       </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>11.438</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>11.309375</t>
-        </is>
+      <c r="AN9" t="n">
+        <v>11.438</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>11.309375</v>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
@@ -4107,15 +4075,11 @@
           <t>11.4275</t>
         </is>
       </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>11.43</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>11.3</t>
-        </is>
+      <c r="AN10" t="n">
+        <v>11.43</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>11.3</v>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
@@ -4494,15 +4458,11 @@
           <t>11.4175</t>
         </is>
       </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>11.425</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>11.291875</t>
-        </is>
+      <c r="AN11" t="n">
+        <v>11.425</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>11.291875</v>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
@@ -4881,15 +4841,11 @@
           <t>87.26500000000001</t>
         </is>
       </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>86.88</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>85.5425</t>
-        </is>
+      <c r="AN12" t="n">
+        <v>86.88</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>85.5425</v>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
@@ -5268,15 +5224,11 @@
           <t>87.045</t>
         </is>
       </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>86.774</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>85.43625</t>
-        </is>
+      <c r="AN13" t="n">
+        <v>86.774</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>85.43625</v>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
@@ -5655,15 +5607,11 @@
           <t>86.86999999999999</t>
         </is>
       </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>86.67</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>85.33250000000001</t>
-        </is>
+      <c r="AN14" t="n">
+        <v>86.67</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>85.33250000000001</v>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
@@ -6042,15 +5990,11 @@
           <t>86.735</t>
         </is>
       </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>86.58800000000001</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>85.24125000000001</t>
-        </is>
+      <c r="AN15" t="n">
+        <v>86.58800000000001</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>85.24125000000001</v>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
@@ -6429,15 +6373,11 @@
           <t>86.615</t>
         </is>
       </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>86.508</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>85.14125</t>
-        </is>
+      <c r="AN16" t="n">
+        <v>86.508</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>85.14125</v>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
@@ -6816,15 +6756,11 @@
           <t>86.47</t>
         </is>
       </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>86.416</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>85.03625</t>
-        </is>
+      <c r="AN17" t="n">
+        <v>86.416</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>85.03625</v>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
@@ -7203,15 +7139,11 @@
           <t>86.33</t>
         </is>
       </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>86.33200000000001</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>84.91875</t>
-        </is>
+      <c r="AN18" t="n">
+        <v>86.33200000000001</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>84.91875</v>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
@@ -7590,15 +7522,11 @@
           <t>86.265</t>
         </is>
       </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>86.27600000000001</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>84.82875</t>
-        </is>
+      <c r="AN19" t="n">
+        <v>86.27600000000001</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>84.82875</v>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
@@ -7977,15 +7905,11 @@
           <t>86.27000000000001</t>
         </is>
       </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>86.22200000000001</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>84.74125</t>
-        </is>
+      <c r="AN20" t="n">
+        <v>86.22200000000001</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>84.74124999999999</v>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
@@ -8364,15 +8288,11 @@
           <t>86.26</t>
         </is>
       </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>86.15799999999999</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>84.65125</t>
-        </is>
+      <c r="AN21" t="n">
+        <v>86.15799999999999</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>84.65125</v>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
@@ -8751,15 +8671,11 @@
           <t>23.5975</t>
         </is>
       </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>22.102</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>21.44625</t>
-        </is>
+      <c r="AN22" t="n">
+        <v>22.102</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>21.44625</v>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
@@ -9138,15 +9054,11 @@
           <t>23.405</t>
         </is>
       </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>22.001</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>21.38375</t>
-        </is>
+      <c r="AN23" t="n">
+        <v>22.001</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>21.38375</v>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
@@ -9525,15 +9437,11 @@
           <t>23.24</t>
         </is>
       </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>21.901</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>21.3275</t>
-        </is>
+      <c r="AN24" t="n">
+        <v>21.901</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>21.3275</v>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
@@ -9912,15 +9820,11 @@
           <t>23.0875</t>
         </is>
       </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>21.807</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>21.275</t>
-        </is>
+      <c r="AN25" t="n">
+        <v>21.807</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>21.275</v>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
@@ -10299,15 +10203,11 @@
           <t>22.9825</t>
         </is>
       </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>21.729</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>21.228125</t>
-        </is>
+      <c r="AN26" t="n">
+        <v>21.729</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>21.228125</v>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
@@ -10686,15 +10586,11 @@
           <t>22.8775</t>
         </is>
       </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>21.65</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>21.183125</t>
-        </is>
+      <c r="AN27" t="n">
+        <v>21.65</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>21.183125</v>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
@@ -11073,15 +10969,11 @@
           <t>22.795</t>
         </is>
       </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>21.584</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>21.1425</t>
-        </is>
+      <c r="AN28" t="n">
+        <v>21.584</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>21.1425</v>
       </c>
       <c r="AP28" t="inlineStr">
         <is>
@@ -11460,15 +11352,11 @@
           <t>22.6925</t>
         </is>
       </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>21.514</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>21.099375</t>
-        </is>
+      <c r="AN29" t="n">
+        <v>21.514</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>21.099375</v>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
@@ -11847,15 +11735,11 @@
           <t>22.6</t>
         </is>
       </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>21.441</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>21.058125</t>
-        </is>
+      <c r="AN30" t="n">
+        <v>21.441</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>21.058125</v>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
@@ -12234,15 +12118,11 @@
           <t>22.5325</t>
         </is>
       </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>21.35899999999999</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>21.01625</t>
-        </is>
+      <c r="AN31" t="n">
+        <v>21.35899999999999</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>21.01625</v>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
@@ -12621,15 +12501,11 @@
           <t>18.86</t>
         </is>
       </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>18.873</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>18.844375</t>
-        </is>
+      <c r="AN32" t="n">
+        <v>18.873</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>18.844375</v>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
@@ -13008,15 +12884,11 @@
           <t>18.8625</t>
         </is>
       </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>18.874</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>18.845625</t>
-        </is>
+      <c r="AN33" t="n">
+        <v>18.874</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>18.845625</v>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
@@ -13395,15 +13267,11 @@
           <t>18.86</t>
         </is>
       </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>18.873</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>18.84625</t>
-        </is>
+      <c r="AN34" t="n">
+        <v>18.873</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>18.84625</v>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
@@ -13782,15 +13650,11 @@
           <t>18.8625</t>
         </is>
       </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>18.873</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>18.846875</t>
-        </is>
+      <c r="AN35" t="n">
+        <v>18.873</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>18.846875</v>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
@@ -14169,15 +14033,11 @@
           <t>18.865</t>
         </is>
       </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>18.873</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>18.846875</t>
-        </is>
+      <c r="AN36" t="n">
+        <v>18.873</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>18.846875</v>
       </c>
       <c r="AP36" t="inlineStr">
         <is>
@@ -14556,15 +14416,11 @@
           <t>18.865</t>
         </is>
       </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>18.872</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>18.846875</t>
-        </is>
+      <c r="AN37" t="n">
+        <v>18.872</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>18.846875</v>
       </c>
       <c r="AP37" t="inlineStr">
         <is>
@@ -14943,15 +14799,11 @@
           <t>18.8625</t>
         </is>
       </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>18.868</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>18.845625</t>
-        </is>
+      <c r="AN38" t="n">
+        <v>18.868</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>18.845625</v>
       </c>
       <c r="AP38" t="inlineStr">
         <is>
@@ -15330,15 +15182,11 @@
           <t>18.8575</t>
         </is>
       </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>18.866</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>18.844375</t>
-        </is>
+      <c r="AN39" t="n">
+        <v>18.866</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>18.844375</v>
       </c>
       <c r="AP39" t="inlineStr">
         <is>
@@ -15717,15 +15565,11 @@
           <t>18.86</t>
         </is>
       </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>18.865</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>18.844375</t>
-        </is>
+      <c r="AN40" t="n">
+        <v>18.865</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>18.844375</v>
       </c>
       <c r="AP40" t="inlineStr">
         <is>
@@ -16104,15 +15948,11 @@
           <t>18.86</t>
         </is>
       </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>18.863</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>18.843125</t>
-        </is>
+      <c r="AN41" t="n">
+        <v>18.863</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>18.843125</v>
       </c>
       <c r="AP41" t="inlineStr">
         <is>
@@ -16491,15 +16331,11 @@
           <t>12.9275</t>
         </is>
       </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>12.663</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>12.29375</t>
-        </is>
+      <c r="AN42" t="n">
+        <v>12.663</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>12.29375</v>
       </c>
       <c r="AP42" t="inlineStr">
         <is>
@@ -16878,15 +16714,11 @@
           <t>12.9475</t>
         </is>
       </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>12.637</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>12.28</t>
-        </is>
+      <c r="AN43" t="n">
+        <v>12.637</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>12.28</v>
       </c>
       <c r="AP43" t="inlineStr">
         <is>
@@ -17265,15 +17097,11 @@
           <t>12.95</t>
         </is>
       </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>12.611</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>12.265625</t>
-        </is>
+      <c r="AN44" t="n">
+        <v>12.611</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>12.265625</v>
       </c>
       <c r="AP44" t="inlineStr">
         <is>
@@ -17652,15 +17480,11 @@
           <t>12.9625</t>
         </is>
       </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>12.584</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>12.25125</t>
-        </is>
+      <c r="AN45" t="n">
+        <v>12.584</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>12.25125</v>
       </c>
       <c r="AP45" t="inlineStr">
         <is>
@@ -18039,15 +17863,11 @@
           <t>12.9775</t>
         </is>
       </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>12.557</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>12.23625</t>
-        </is>
+      <c r="AN46" t="n">
+        <v>12.557</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>12.23625</v>
       </c>
       <c r="AP46" t="inlineStr">
         <is>
@@ -18426,15 +18246,11 @@
           <t>12.9825</t>
         </is>
       </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>12.528</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>12.22</t>
-        </is>
+      <c r="AN47" t="n">
+        <v>12.528</v>
+      </c>
+      <c r="AO47" t="n">
+        <v>12.22</v>
       </c>
       <c r="AP47" t="inlineStr">
         <is>
@@ -18813,15 +18629,11 @@
           <t>12.9875</t>
         </is>
       </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>12.502</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>12.20375</t>
-        </is>
+      <c r="AN48" t="n">
+        <v>12.502</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>12.20375</v>
       </c>
       <c r="AP48" t="inlineStr">
         <is>
@@ -19200,15 +19012,11 @@
           <t>12.985</t>
         </is>
       </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>12.474</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>12.188125</t>
-        </is>
+      <c r="AN49" t="n">
+        <v>12.474</v>
+      </c>
+      <c r="AO49" t="n">
+        <v>12.188125</v>
       </c>
       <c r="AP49" t="inlineStr">
         <is>
@@ -19587,15 +19395,11 @@
           <t>12.99</t>
         </is>
       </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>12.44</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>12.1725</t>
-        </is>
+      <c r="AN50" t="n">
+        <v>12.44</v>
+      </c>
+      <c r="AO50" t="n">
+        <v>12.1725</v>
       </c>
       <c r="AP50" t="inlineStr">
         <is>
@@ -19974,15 +19778,11 @@
           <t>12.9975</t>
         </is>
       </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>12.406</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>12.156875</t>
-        </is>
+      <c r="AN51" t="n">
+        <v>12.406</v>
+      </c>
+      <c r="AO51" t="n">
+        <v>12.156875</v>
       </c>
       <c r="AP51" t="inlineStr">
         <is>
@@ -20361,15 +20161,11 @@
           <t>10.98</t>
         </is>
       </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>10.982</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>10.958125</t>
-        </is>
+      <c r="AN52" t="n">
+        <v>10.982</v>
+      </c>
+      <c r="AO52" t="n">
+        <v>10.958125</v>
       </c>
       <c r="AP52" t="inlineStr">
         <is>
@@ -20748,15 +20544,11 @@
           <t>10.9775</t>
         </is>
       </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>10.985</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>10.9575</t>
-        </is>
+      <c r="AN53" t="n">
+        <v>10.985</v>
+      </c>
+      <c r="AO53" t="n">
+        <v>10.9575</v>
       </c>
       <c r="AP53" t="inlineStr">
         <is>
@@ -21135,15 +20927,11 @@
           <t>10.98</t>
         </is>
       </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>10.988</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>10.956875</t>
-        </is>
+      <c r="AN54" t="n">
+        <v>10.988</v>
+      </c>
+      <c r="AO54" t="n">
+        <v>10.956875</v>
       </c>
       <c r="AP54" t="inlineStr">
         <is>
@@ -21522,15 +21310,11 @@
           <t>10.985</t>
         </is>
       </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>10.989</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>10.955</t>
-        </is>
+      <c r="AN55" t="n">
+        <v>10.989</v>
+      </c>
+      <c r="AO55" t="n">
+        <v>10.955</v>
       </c>
       <c r="AP55" t="inlineStr">
         <is>
@@ -21909,15 +21693,11 @@
           <t>10.985</t>
         </is>
       </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>10.99</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>10.95125</t>
-        </is>
+      <c r="AN56" t="n">
+        <v>10.99</v>
+      </c>
+      <c r="AO56" t="n">
+        <v>10.95125</v>
       </c>
       <c r="AP56" t="inlineStr">
         <is>
@@ -22296,15 +22076,11 @@
           <t>10.9825</t>
         </is>
       </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>10.992</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>10.9475</t>
-        </is>
+      <c r="AN57" t="n">
+        <v>10.992</v>
+      </c>
+      <c r="AO57" t="n">
+        <v>10.9475</v>
       </c>
       <c r="AP57" t="inlineStr">
         <is>
@@ -22683,15 +22459,11 @@
           <t>10.98</t>
         </is>
       </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>10.994</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>10.945625</t>
-        </is>
+      <c r="AN58" t="n">
+        <v>10.994</v>
+      </c>
+      <c r="AO58" t="n">
+        <v>10.945625</v>
       </c>
       <c r="AP58" t="inlineStr">
         <is>
@@ -23070,15 +22842,11 @@
           <t>10.9775</t>
         </is>
       </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>10.997</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>10.94375</t>
-        </is>
+      <c r="AN59" t="n">
+        <v>10.997</v>
+      </c>
+      <c r="AO59" t="n">
+        <v>10.94375</v>
       </c>
       <c r="AP59" t="inlineStr">
         <is>
@@ -23457,15 +23225,11 @@
           <t>10.9775</t>
         </is>
       </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>11.003</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>10.94125</t>
-        </is>
+      <c r="AN60" t="n">
+        <v>11.003</v>
+      </c>
+      <c r="AO60" t="n">
+        <v>10.94125</v>
       </c>
       <c r="AP60" t="inlineStr">
         <is>
@@ -23844,15 +23608,11 @@
           <t>10.975</t>
         </is>
       </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>11.011</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>10.939375</t>
-        </is>
+      <c r="AN61" t="n">
+        <v>11.011</v>
+      </c>
+      <c r="AO61" t="n">
+        <v>10.939375</v>
       </c>
       <c r="AP61" t="inlineStr">
         <is>
@@ -24231,15 +23991,11 @@
           <t>41.09500000000001</t>
         </is>
       </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>41.63</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>41.634375</t>
-        </is>
+      <c r="AN62" t="n">
+        <v>41.63</v>
+      </c>
+      <c r="AO62" t="n">
+        <v>41.634375</v>
       </c>
       <c r="AP62" t="inlineStr">
         <is>
@@ -24618,15 +24374,11 @@
           <t>41.135</t>
         </is>
       </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>41.657</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>41.63875</t>
-        </is>
+      <c r="AN63" t="n">
+        <v>41.657</v>
+      </c>
+      <c r="AO63" t="n">
+        <v>41.63875</v>
       </c>
       <c r="AP63" t="inlineStr">
         <is>
@@ -25005,15 +24757,11 @@
           <t>41.15</t>
         </is>
       </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>41.677</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>41.63875</t>
-        </is>
+      <c r="AN64" t="n">
+        <v>41.677</v>
+      </c>
+      <c r="AO64" t="n">
+        <v>41.63875</v>
       </c>
       <c r="AP64" t="inlineStr">
         <is>
@@ -25392,15 +25140,11 @@
           <t>41.1625</t>
         </is>
       </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>41.703</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>41.6375</t>
-        </is>
+      <c r="AN65" t="n">
+        <v>41.703</v>
+      </c>
+      <c r="AO65" t="n">
+        <v>41.6375</v>
       </c>
       <c r="AP65" t="inlineStr">
         <is>
@@ -25779,15 +25523,11 @@
           <t>41.19750000000001</t>
         </is>
       </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>41.731</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>41.63875</t>
-        </is>
+      <c r="AN66" t="n">
+        <v>41.731</v>
+      </c>
+      <c r="AO66" t="n">
+        <v>41.63875</v>
       </c>
       <c r="AP66" t="inlineStr">
         <is>
@@ -26166,15 +25906,11 @@
           <t>41.235</t>
         </is>
       </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>41.75</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>41.640625</t>
-        </is>
+      <c r="AN67" t="n">
+        <v>41.75</v>
+      </c>
+      <c r="AO67" t="n">
+        <v>41.640625</v>
       </c>
       <c r="AP67" t="inlineStr">
         <is>
@@ -26553,15 +26289,11 @@
           <t>41.2725</t>
         </is>
       </c>
-      <c r="AN68" t="inlineStr">
-        <is>
-          <t>41.768</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>41.64125</t>
-        </is>
+      <c r="AN68" t="n">
+        <v>41.768</v>
+      </c>
+      <c r="AO68" t="n">
+        <v>41.64125</v>
       </c>
       <c r="AP68" t="inlineStr">
         <is>
@@ -26940,15 +26672,11 @@
           <t>41.3125</t>
         </is>
       </c>
-      <c r="AN69" t="inlineStr">
-        <is>
-          <t>41.78</t>
-        </is>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>41.64375</t>
-        </is>
+      <c r="AN69" t="n">
+        <v>41.78</v>
+      </c>
+      <c r="AO69" t="n">
+        <v>41.64375</v>
       </c>
       <c r="AP69" t="inlineStr">
         <is>
@@ -27327,15 +27055,11 @@
           <t>41.3575</t>
         </is>
       </c>
-      <c r="AN70" t="inlineStr">
-        <is>
-          <t>41.79</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>41.65062500000001</t>
-        </is>
+      <c r="AN70" t="n">
+        <v>41.79</v>
+      </c>
+      <c r="AO70" t="n">
+        <v>41.65062500000001</v>
       </c>
       <c r="AP70" t="inlineStr">
         <is>
@@ -27714,15 +27438,11 @@
           <t>41.395</t>
         </is>
       </c>
-      <c r="AN71" t="inlineStr">
-        <is>
-          <t>41.79599999999999</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>41.65625</t>
-        </is>
+      <c r="AN71" t="n">
+        <v>41.79599999999999</v>
+      </c>
+      <c r="AO71" t="n">
+        <v>41.65625</v>
       </c>
       <c r="AP71" t="inlineStr">
         <is>
@@ -28101,15 +27821,11 @@
           <t>15.05</t>
         </is>
       </c>
-      <c r="AN72" t="inlineStr">
-        <is>
-          <t>14.345</t>
-        </is>
-      </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>13.505625</t>
-        </is>
+      <c r="AN72" t="n">
+        <v>14.345</v>
+      </c>
+      <c r="AO72" t="n">
+        <v>13.505625</v>
       </c>
       <c r="AP72" t="inlineStr">
         <is>
@@ -28488,15 +28204,11 @@
           <t>14.97</t>
         </is>
       </c>
-      <c r="AN73" t="inlineStr">
-        <is>
-          <t>14.283</t>
-        </is>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>13.45625</t>
-        </is>
+      <c r="AN73" t="n">
+        <v>14.283</v>
+      </c>
+      <c r="AO73" t="n">
+        <v>13.45625</v>
       </c>
       <c r="AP73" t="inlineStr">
         <is>
@@ -28875,15 +28587,11 @@
           <t>14.8725</t>
         </is>
       </c>
-      <c r="AN74" t="inlineStr">
-        <is>
-          <t>14.213</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>13.405625</t>
-        </is>
+      <c r="AN74" t="n">
+        <v>14.213</v>
+      </c>
+      <c r="AO74" t="n">
+        <v>13.405625</v>
       </c>
       <c r="AP74" t="inlineStr">
         <is>
@@ -29262,15 +28970,11 @@
           <t>14.78</t>
         </is>
       </c>
-      <c r="AN75" t="inlineStr">
-        <is>
-          <t>14.144</t>
-        </is>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>13.37125</t>
-        </is>
+      <c r="AN75" t="n">
+        <v>14.144</v>
+      </c>
+      <c r="AO75" t="n">
+        <v>13.37125</v>
       </c>
       <c r="AP75" t="inlineStr">
         <is>
@@ -29649,15 +29353,11 @@
           <t>14.695</t>
         </is>
       </c>
-      <c r="AN76" t="inlineStr">
-        <is>
-          <t>14.078</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>13.3375</t>
-        </is>
+      <c r="AN76" t="n">
+        <v>14.078</v>
+      </c>
+      <c r="AO76" t="n">
+        <v>13.3375</v>
       </c>
       <c r="AP76" t="inlineStr">
         <is>
@@ -30036,15 +29736,11 @@
           <t>14.62</t>
         </is>
       </c>
-      <c r="AN77" t="inlineStr">
-        <is>
-          <t>14.017</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>13.30875</t>
-        </is>
+      <c r="AN77" t="n">
+        <v>14.017</v>
+      </c>
+      <c r="AO77" t="n">
+        <v>13.30875</v>
       </c>
       <c r="AP77" t="inlineStr">
         <is>
@@ -30423,15 +30119,11 @@
           <t>14.5575</t>
         </is>
       </c>
-      <c r="AN78" t="inlineStr">
-        <is>
-          <t>13.965</t>
-        </is>
-      </c>
-      <c r="AO78" t="inlineStr">
-        <is>
-          <t>13.285625</t>
-        </is>
+      <c r="AN78" t="n">
+        <v>13.965</v>
+      </c>
+      <c r="AO78" t="n">
+        <v>13.285625</v>
       </c>
       <c r="AP78" t="inlineStr">
         <is>
@@ -30810,15 +30502,11 @@
           <t>14.5</t>
         </is>
       </c>
-      <c r="AN79" t="inlineStr">
-        <is>
-          <t>13.917</t>
-        </is>
-      </c>
-      <c r="AO79" t="inlineStr">
-        <is>
-          <t>13.26375</t>
-        </is>
+      <c r="AN79" t="n">
+        <v>13.917</v>
+      </c>
+      <c r="AO79" t="n">
+        <v>13.26375</v>
       </c>
       <c r="AP79" t="inlineStr">
         <is>
@@ -31197,15 +30885,11 @@
           <t>14.445</t>
         </is>
       </c>
-      <c r="AN80" t="inlineStr">
-        <is>
-          <t>13.867</t>
-        </is>
-      </c>
-      <c r="AO80" t="inlineStr">
-        <is>
-          <t>13.240625</t>
-        </is>
+      <c r="AN80" t="n">
+        <v>13.867</v>
+      </c>
+      <c r="AO80" t="n">
+        <v>13.240625</v>
       </c>
       <c r="AP80" t="inlineStr">
         <is>
@@ -31584,15 +31268,11 @@
           <t>14.38</t>
         </is>
       </c>
-      <c r="AN81" t="inlineStr">
-        <is>
-          <t>13.82</t>
-        </is>
-      </c>
-      <c r="AO81" t="inlineStr">
-        <is>
-          <t>13.221875</t>
-        </is>
+      <c r="AN81" t="n">
+        <v>13.82</v>
+      </c>
+      <c r="AO81" t="n">
+        <v>13.221875</v>
       </c>
       <c r="AP81" t="inlineStr">
         <is>

--- a/Result/checksun/金融業.xlsx
+++ b/Result/checksun/金融業.xlsx
@@ -14931,7 +14931,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>價_量;【d1】;【d2】</t>
+          <t>價_量;【d1】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15357,7 +15357,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15783,7 +15783,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16207,7 +16207,11 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr"/>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
           <t>6020</t>
@@ -16629,7 +16633,11 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr"/>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>6020</t>
@@ -19609,7 +19617,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20035,7 +20043,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20461,7 +20469,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -20887,7 +20895,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21313,7 +21321,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21737,7 +21745,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr"/>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
           <t>6016</t>
@@ -24291,7 +24303,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -24715,7 +24727,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr"/>
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
           <t>6015</t>
@@ -25137,7 +25153,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr"/>
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
           <t>6015</t>
@@ -25559,7 +25579,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr"/>
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
           <t>6015</t>
@@ -28963,7 +28987,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr"/>
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B68" t="inlineStr">
         <is>
           <t>5878</t>
@@ -29385,7 +29413,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr"/>
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
           <t>5878</t>
